--- a/excel_routes/route_CCE_AJF_threats.xlsx
+++ b/excel_routes/route_CCE_AJF_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10830</v>
+        <v>6763</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11630</v>
+        <v>7341</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-800</v>
+        <v>-578</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -582,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10830</v>
+        <v>7242</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11630</v>
+        <v>7341</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-800</v>
+        <v>-99</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -613,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -627,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7701</v>
+        <v>6763</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7940</v>
+        <v>7341</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-239</v>
+        <v>-578</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -658,27 +676,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-321</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7701</v>
+        <v>7242</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7940</v>
+        <v>7341</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-239</v>
+        <v>-99</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -703,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>18-APR-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-209</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6748</v>
+        <v>9525</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6790</v>
+        <v>15767</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-42</v>
+        <v>-6242</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -734,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -748,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>18-APR-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -758,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-209</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6748</v>
+        <v>7467</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6790</v>
+        <v>7538</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-42</v>
+        <v>-71</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -793,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7926</v>
+        <v>7467</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8347</v>
+        <v>7538</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-421</v>
+        <v>-71</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -838,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7926</v>
+        <v>7721</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8347</v>
+        <v>7735</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-421</v>
+        <v>-14</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -883,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -897,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10830</v>
+        <v>7721</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13004</v>
+        <v>7735</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2174</v>
+        <v>-14</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -928,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -938,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10830</v>
+        <v>7467</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13004</v>
+        <v>7735</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-2174</v>
+        <v>-268</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -973,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -983,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10830</v>
+        <v>7467</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13004</v>
+        <v>7735</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2174</v>
+        <v>-268</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1018,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1032,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10830</v>
+        <v>8679</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13004</v>
+        <v>9708</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-2174</v>
+        <v>-1029</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1063,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1077,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10830</v>
+        <v>8679</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13004</v>
+        <v>9708</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2174</v>
+        <v>-1029</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1108,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1118,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10830</v>
+        <v>10835</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13004</v>
+        <v>12188</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-2174</v>
+        <v>-1353</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1153,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1167,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7449</v>
+        <v>10835</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7786</v>
+        <v>13568</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-337</v>
+        <v>-2733</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1198,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1208,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7449</v>
+        <v>10835</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7786</v>
+        <v>13568</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-337</v>
+        <v>-2733</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1243,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1253,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7449</v>
+        <v>9525</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7940</v>
+        <v>12188</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-491</v>
+        <v>-2663</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1288,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1302,13 +1320,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7449</v>
+        <v>9525</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7940</v>
+        <v>11314</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-491</v>
+        <v>-1789</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1333,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1347,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7449</v>
+        <v>8679</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>7786</v>
+        <v>13568</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-337</v>
+        <v>-4889</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1364,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1378,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1392,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7449</v>
+        <v>8679</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>7786</v>
+        <v>13568</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-337</v>
+        <v>-4889</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1409,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1423,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1437,13 +1455,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7449</v>
+        <v>7721</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>7940</v>
+        <v>13568</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-491</v>
+        <v>-5847</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1454,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1468,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1478,33 +1496,213 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>7467</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>13568</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-6101</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>Nile Air NP-109</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>7449</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>7940</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-491</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="n">
+        <v>7467</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>13568</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-6101</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>7467</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>8341</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-874</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-109</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>7467</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>8341</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-874</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>30-SEP-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-321</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-119</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>7467</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>8482</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-1015</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CCE_AJF_threats.xlsx
+++ b/excel_routes/route_CCE_AJF_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6763</v>
+        <v>4894</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7341</v>
+        <v>4908</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-578</v>
+        <v>-14</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7242</v>
+        <v>4894</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7341</v>
+        <v>4908</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-99</v>
+        <v>-14</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,27 +631,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-321</t>
+          <t>SM-973</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6763</v>
+        <v>4894</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7341</v>
+        <v>4908</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-578</v>
+        <v>-14</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,12 +676,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-973</t>
+          <t>SM-321</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7242</v>
+        <v>10724</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7341</v>
+        <v>14043</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-99</v>
+        <v>-3319</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9525</v>
+        <v>10724</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15767</v>
+        <v>11100</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-6242</v>
+        <v>-376</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7467</v>
+        <v>9399</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7538</v>
+        <v>10110</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-71</v>
+        <v>-711</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7467</v>
+        <v>7614</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7538</v>
+        <v>7642</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-71</v>
+        <v>-28</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7721</v>
+        <v>8339</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7735</v>
+        <v>9120</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-14</v>
+        <v>-781</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7721</v>
+        <v>8339</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7735</v>
+        <v>9120</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-14</v>
+        <v>-781</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7467</v>
+        <v>8562</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7735</v>
+        <v>14043</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-268</v>
+        <v>-5481</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7467</v>
+        <v>8562</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7735</v>
+        <v>14043</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-268</v>
+        <v>-5481</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8679</v>
+        <v>10724</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>9708</v>
+        <v>16511</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1029</v>
+        <v>-5787</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8679</v>
+        <v>14294</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9708</v>
+        <v>20444</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1029</v>
+        <v>-6150</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10835</v>
+        <v>10724</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12188</v>
+        <v>16511</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1353</v>
+        <v>-5787</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10835</v>
+        <v>10724</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13568</v>
+        <v>16511</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-2733</v>
+        <v>-5787</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>10835</v>
+        <v>9399</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>13568</v>
+        <v>15033</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-2733</v>
+        <v>-5634</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1247,9 +1247,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9525</v>
+        <v>8562</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>12188</v>
+        <v>16511</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-2663</v>
+        <v>-7949</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1292,9 +1292,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-109</t>
+          <t>Nile Air NP-119</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9525</v>
+        <v>8562</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11314</v>
+        <v>16511</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1789</v>
+        <v>-7949</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-119</t>
+          <t>Nile Air NP-109</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8679</v>
+        <v>7391</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>13568</v>
+        <v>16511</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4889</v>
+        <v>-9120</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8679</v>
+        <v>7391</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13568</v>
+        <v>16511</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-4889</v>
+        <v>-9120</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7721</v>
+        <v>7391</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>13568</v>
+        <v>16511</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-5847</v>
+        <v>-9120</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1472,7 +1472,7 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7467</v>
+        <v>7391</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>13568</v>
+        <v>9120</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-6101</v>
+        <v>-1729</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7467</v>
+        <v>7391</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>13568</v>
+        <v>9120</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-6101</v>
+        <v>-1729</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1562,9 +1562,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>30-SEP-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7467</v>
+        <v>7391</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>8341</v>
+        <v>10110</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-874</v>
+        <v>-2719</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1613,96 +1613,6 @@
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-109</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>7467</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>8341</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-874</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>30-SEP-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-321</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-119</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>7467</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>8482</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-1015</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
